--- a/application/static/excel/Log.xlsx
+++ b/application/static/excel/Log.xlsx
@@ -3,20 +3,20 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,12 +30,6 @@
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -444,11 +438,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
-  </cols>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -483,6 +474,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>File Name</t>
         </is>
       </c>
@@ -490,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020-12-22</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:09:44</t>
+          <t>09:19:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -514,58 +510,68 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2020-12-22_ARM_A_C100-LHD_1_ver1.xlsx</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2020-12-30_ARM_A_C100-LHD_100_ver1.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020-12-22</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:15:49</t>
+          <t>10:02:05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C100 LHD</t>
+          <t>LFD</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2020-12-22_ASS_C_C100-LHD_1_ver3.xlsx</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2020-12-30_ARM_A_LFD_10_ver1.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2020-12-22</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:16:13</t>
+          <t>11:22:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -575,7 +581,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -584,23 +590,28 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2020-12-22_ARM_B_X100_33_ver12.xlsx</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2020-12-30_ARM_C_X100_10_ver1.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2020-12-22</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:16:20</t>
+          <t>11:22:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -610,270 +621,109 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>LFD</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2020-12-22_ARM_E_X100_43_ver23.xlsx</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2020-12-30_ARM_A_LFD_100_ver1.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2020-12-22</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:16:30</t>
+          <t>11:24:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Doowon AB</t>
+          <t>CD6</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2020-12-22_ARM_J_Doowon-AB_43_ver123.xlsx</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2020-12-30_ASS_A_CD6_100_ver1.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2020-12-23</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:16:40</t>
+          <t>13:47:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Doowon AB</t>
+          <t>C100 LHD</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2020-12-22_ARM_J_Doowon-AB_64_ver123.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2020-12-24</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>10:16:50</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ARM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Doowon AB</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>766</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2020-12-22_ARM_J_Doowon-AB_766_ver123.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2020-12-25</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>10:16:60</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ARM</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Doowon AB</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>5656</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2020-12-22_ARM_J_Doowon-AB_5656_ver123.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2020-12-26</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>10:16:70</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ARM</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Doowon AB</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>44</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2020-12-22_ARM_J_Doowon-AB_44_ver123.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2020-12-22</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>16:37:49</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ASS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Sanden</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2020-12-22_ASS_C_Sanden_3_ver23.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2020-12-22</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>16:38:09</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ASS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LJL</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2020-12-22_ASS_F_LJL_4_ver3.xlsx</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2020-12-30_ASS_D_C100-LHD_100_ver1.xlsx</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="256" horizontalDpi="203" verticalDpi="203"/>
 </worksheet>
 </file>